--- a/Biotherm_daily_totals.xlsx
+++ b/Biotherm_daily_totals.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Shared\Documents\SMaS\Client Campaigns\2026\DE\Biotherm Jun\Review\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F3E584D-9F33-4591-AB26-236B99E45630}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE26DD60-E321-48F1-915B-DADF50F08E7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-22350" yWindow="-1980" windowWidth="19200" windowHeight="11265" xr2:uid="{2851D042-8A40-455A-A0A9-C423A6CE23DE}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" xr2:uid="{2851D042-8A40-455A-A0A9-C423A6CE23DE}"/>
   </bookViews>
   <sheets>
     <sheet name="Daily Totals" sheetId="1" r:id="rId1"/>
@@ -510,7 +510,15 @@
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8" s="1"/>
+      <c r="A8" s="1">
+        <v>46195</v>
+      </c>
+      <c r="B8">
+        <v>124</v>
+      </c>
+      <c r="C8">
+        <v>64</v>
+      </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="1"/>

--- a/Biotherm_daily_totals.xlsx
+++ b/Biotherm_daily_totals.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Shared\Documents\SMaS\Client Campaigns\2026\DE\Biotherm Jun\Review\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE26DD60-E321-48F1-915B-DADF50F08E7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CE8FFAF-EA3C-4C3D-B1DF-B116A730E022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" xr2:uid="{2851D042-8A40-455A-A0A9-C423A6CE23DE}"/>
   </bookViews>
@@ -521,7 +521,15 @@
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9" s="1"/>
+      <c r="A9" s="1">
+        <v>46196</v>
+      </c>
+      <c r="B9">
+        <v>141</v>
+      </c>
+      <c r="C9">
+        <v>74</v>
+      </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="1"/>

--- a/Biotherm_daily_totals.xlsx
+++ b/Biotherm_daily_totals.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Shared\Documents\SMaS\Client Campaigns\2026\DE\Biotherm Jun\Review\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CE8FFAF-EA3C-4C3D-B1DF-B116A730E022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3802168-E861-4E0F-B53A-43F2488A143F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" xr2:uid="{2851D042-8A40-455A-A0A9-C423A6CE23DE}"/>
   </bookViews>
@@ -532,7 +532,15 @@
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A10" s="1"/>
+      <c r="A10" s="1">
+        <v>46197</v>
+      </c>
+      <c r="B10">
+        <v>157</v>
+      </c>
+      <c r="C10">
+        <v>71</v>
+      </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="1"/>

--- a/Biotherm_daily_totals.xlsx
+++ b/Biotherm_daily_totals.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Shared\Documents\SMaS\Client Campaigns\2026\DE\Biotherm Jun\Review\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3802168-E861-4E0F-B53A-43F2488A143F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAEF2467-3E95-4EDB-8A62-0C2CCDA4FEB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" xr2:uid="{2851D042-8A40-455A-A0A9-C423A6CE23DE}"/>
   </bookViews>
@@ -543,10 +543,26 @@
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A11" s="1"/>
+      <c r="A11" s="1">
+        <v>46198</v>
+      </c>
+      <c r="B11">
+        <v>161</v>
+      </c>
+      <c r="C11">
+        <v>80</v>
+      </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A12" s="1"/>
+      <c r="A12" s="1">
+        <v>46199</v>
+      </c>
+      <c r="B12">
+        <v>179</v>
+      </c>
+      <c r="C12">
+        <v>77</v>
+      </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="1"/>

--- a/Biotherm_daily_totals.xlsx
+++ b/Biotherm_daily_totals.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Shared\Documents\SMaS\Client Campaigns\2026\DE\Biotherm Jun\Review\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAEF2467-3E95-4EDB-8A62-0C2CCDA4FEB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EC5FAF3-C94F-471B-B472-416E24CE8D22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" xr2:uid="{2851D042-8A40-455A-A0A9-C423A6CE23DE}"/>
+    <workbookView xWindow="-28920" yWindow="-3870" windowWidth="29040" windowHeight="15840" xr2:uid="{2851D042-8A40-455A-A0A9-C423A6CE23DE}"/>
   </bookViews>
   <sheets>
     <sheet name="Daily Totals" sheetId="1" r:id="rId1"/>
@@ -565,10 +565,26 @@
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A13" s="1"/>
+      <c r="A13" s="1">
+        <v>46200</v>
+      </c>
+      <c r="B13">
+        <v>177</v>
+      </c>
+      <c r="C13">
+        <v>65</v>
+      </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A14" s="1"/>
+      <c r="A14" s="1">
+        <v>46201</v>
+      </c>
+      <c r="B14">
+        <v>168</v>
+      </c>
+      <c r="C14">
+        <v>63</v>
+      </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" s="1"/>

--- a/Biotherm_daily_totals.xlsx
+++ b/Biotherm_daily_totals.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Shared\Documents\SMaS\Client Campaigns\2026\DE\Biotherm Jun\Review\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EC5FAF3-C94F-471B-B472-416E24CE8D22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6817A0D-61C3-48FF-B1B6-2A1517F8C7E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-3870" windowWidth="29040" windowHeight="15840" xr2:uid="{2851D042-8A40-455A-A0A9-C423A6CE23DE}"/>
   </bookViews>
@@ -587,10 +587,26 @@
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A15" s="1"/>
+      <c r="A15" s="1">
+        <v>46202</v>
+      </c>
+      <c r="B15">
+        <v>174</v>
+      </c>
+      <c r="C15">
+        <v>61</v>
+      </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A16" s="1"/>
+      <c r="A16" s="1">
+        <v>46203</v>
+      </c>
+      <c r="B16">
+        <v>189</v>
+      </c>
+      <c r="C16">
+        <v>70</v>
+      </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A17" s="1"/>
